--- a/Result/profitability/1309.xlsx
+++ b/Result/profitability/1309.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.23875</v>
+        <v>-0.28875</v>
       </c>
       <c r="N2" t="n">
-        <v>3.805</v>
+        <v>3.92375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.55</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.13875</v>
+        <v>-0.225</v>
       </c>
       <c r="N3" t="n">
-        <v>3.87375</v>
+        <v>4.025</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -795,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.52</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.20875</v>
+        <v>-0.2725</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9125</v>
+        <v>3.23625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-5.45</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.8775000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.49</v>
+        <v>-4.06</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.52</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.73125</v>
+        <v>-0.79</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.63</v>
+        <v>-3.1525</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6212500000000001</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.777500000000001</v>
+        <v>-2.245000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.51</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.54</v>
+        <v>-0.5550000000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.36875</v>
+        <v>-1.20625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.44875</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3825</v>
+        <v>-1.382500000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>-0.38125</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8100000000000004</v>
+        <v>-0.8100000000000006</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.45875</v>
+        <v>-0.4587500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>-1.272500000000001</v>
@@ -1902,7 +1902,7 @@
         <v>-0.29875</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2000000000000004</v>
+        <v>-0.2000000000000006</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2840</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2626</v>
+      </c>
+      <c r="E75" t="n">
+        <v>214</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-159</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.60%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-174</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-333</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-257</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.3075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.34375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2264150943396226</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-5.284090909090909</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.06557377049180335</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.8390243902439025</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
